--- a/public/uploads/vouchers/Single_claimable_Voucher.xlsx
+++ b/public/uploads/vouchers/Single_claimable_Voucher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Financial_System\financial-app\public\uploads\vouchers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EFCDD5-66A1-40D0-8E6E-827DBF27A3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8591F1-502D-46A6-9748-3E4E6DE7D667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>slip#</t>
   </si>
@@ -127,6 +125,12 @@
   <si>
     <t>ghejensksnsisnisnsi</t>
   </si>
+  <si>
+    <t>dda</t>
+  </si>
+  <si>
+    <t>fdfs</t>
+  </si>
 </sst>
 </file>
 
@@ -149,39 +153,39 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -189,34 +193,34 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Lucida Bright"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -224,7 +228,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Lucida Bright"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -561,10 +565,17 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -577,21 +588,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1368,13 +1372,13 @@
       <c r="H9" s="37"/>
       <c r="I9" s="37"/>
       <c r="J9" s="38"/>
-      <c r="K9" s="56" t="s">
+      <c r="K9" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="58" t="s">
+      <c r="L9" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="60" t="s">
+      <c r="M9" s="54" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="37"/>
@@ -1407,9 +1411,9 @@
       <c r="H10" s="43"/>
       <c r="I10" s="43"/>
       <c r="J10" s="47"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="61"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="55"/>
       <c r="N10" s="43"/>
       <c r="O10" s="43"/>
       <c r="P10" s="43"/>
@@ -1438,7 +1442,7 @@
       <c r="H11" s="34"/>
       <c r="I11" s="34"/>
       <c r="J11" s="35"/>
-      <c r="K11" s="62" t="s">
+      <c r="K11" s="63" t="s">
         <v>22</v>
       </c>
       <c r="L11" s="38"/>
@@ -1491,7 +1495,7 @@
       <c r="J12" s="19">
         <v>13</v>
       </c>
-      <c r="K12" s="61"/>
+      <c r="K12" s="55"/>
       <c r="L12" s="47"/>
       <c r="M12" s="19">
         <v>16</v>
@@ -1528,7 +1532,7 @@
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="24" customHeight="1">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="57" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="37"/>
@@ -1540,11 +1544,13 @@
       <c r="H13" s="37"/>
       <c r="I13" s="37"/>
       <c r="J13" s="38"/>
-      <c r="K13" s="63"/>
+      <c r="K13" s="57" t="s">
+        <v>31</v>
+      </c>
       <c r="L13" s="38"/>
       <c r="M13" s="36"/>
       <c r="N13" s="38"/>
-      <c r="O13" s="65"/>
+      <c r="O13" s="56"/>
       <c r="P13" s="37"/>
       <c r="Q13" s="37"/>
       <c r="R13" s="37"/>
@@ -1569,11 +1575,11 @@
       <c r="H14" s="40"/>
       <c r="I14" s="40"/>
       <c r="J14" s="41"/>
-      <c r="K14" s="61"/>
+      <c r="K14" s="55"/>
       <c r="L14" s="47"/>
-      <c r="M14" s="61"/>
+      <c r="M14" s="55"/>
       <c r="N14" s="47"/>
-      <c r="O14" s="61"/>
+      <c r="O14" s="55"/>
       <c r="P14" s="43"/>
       <c r="Q14" s="43"/>
       <c r="R14" s="43"/>
@@ -1581,17 +1587,14 @@
       <c r="T14" s="43"/>
       <c r="U14" s="47"/>
       <c r="V14" s="15"/>
-      <c r="W14" s="20">
-        <f>1374.37/0.12</f>
-        <v>11453.083333333299</v>
-      </c>
+      <c r="W14" s="15"/>
       <c r="X14" s="15"/>
       <c r="Y14" s="15"/>
       <c r="Z14" s="15"/>
       <c r="AA14" s="15"/>
     </row>
     <row r="15" spans="1:27" ht="24" customHeight="1">
-      <c r="A15" s="61"/>
+      <c r="A15" s="55"/>
       <c r="B15" s="43"/>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -1601,7 +1604,9 @@
       <c r="H15" s="43"/>
       <c r="I15" s="43"/>
       <c r="J15" s="47"/>
-      <c r="K15" s="51"/>
+      <c r="K15" s="51" t="s">
+        <v>32</v>
+      </c>
       <c r="L15" s="35"/>
       <c r="M15" s="52"/>
       <c r="N15" s="35"/>
@@ -1613,10 +1618,7 @@
       <c r="T15" s="34"/>
       <c r="U15" s="35"/>
       <c r="V15" s="15"/>
-      <c r="W15" s="20">
-        <f>W14*1.12</f>
-        <v>12827.4533333333</v>
-      </c>
+      <c r="W15" s="15"/>
       <c r="X15" s="15"/>
       <c r="Y15" s="15"/>
       <c r="Z15" s="15"/>
@@ -1633,7 +1635,7 @@
       <c r="H16" s="21"/>
       <c r="I16" s="21"/>
       <c r="J16" s="21"/>
-      <c r="K16" s="54"/>
+      <c r="K16" s="65"/>
       <c r="L16" s="35"/>
       <c r="M16" s="22"/>
       <c r="N16" s="23"/>
@@ -1646,10 +1648,7 @@
       <c r="U16" s="35"/>
       <c r="V16" s="15"/>
       <c r="W16" s="15"/>
-      <c r="X16" s="15">
-        <f>12827.5-1374.37</f>
-        <v>11453.13</v>
-      </c>
+      <c r="X16" s="15"/>
       <c r="Y16" s="15"/>
       <c r="Z16" s="15"/>
       <c r="AA16" s="15"/>
@@ -1665,11 +1664,11 @@
       <c r="H17" s="21"/>
       <c r="I17" s="21"/>
       <c r="J17" s="21"/>
-      <c r="K17" s="54"/>
+      <c r="K17" s="65"/>
       <c r="L17" s="35"/>
       <c r="M17" s="24"/>
       <c r="N17" s="25"/>
-      <c r="O17" s="55"/>
+      <c r="O17" s="66"/>
       <c r="P17" s="34"/>
       <c r="Q17" s="34"/>
       <c r="R17" s="34"/>
@@ -1679,10 +1678,7 @@
       <c r="V17" s="15"/>
       <c r="W17" s="15"/>
       <c r="X17" s="15"/>
-      <c r="Y17" s="15">
-        <f>4308/1.12</f>
-        <v>3846.4285714285702</v>
-      </c>
+      <c r="Y17" s="15"/>
       <c r="Z17" s="15"/>
       <c r="AA17" s="15"/>
     </row>
@@ -1697,11 +1693,11 @@
       <c r="H18" s="21"/>
       <c r="I18" s="21"/>
       <c r="J18" s="21"/>
-      <c r="K18" s="54"/>
+      <c r="K18" s="65"/>
       <c r="L18" s="35"/>
       <c r="M18" s="24"/>
       <c r="N18" s="25"/>
-      <c r="O18" s="55"/>
+      <c r="O18" s="66"/>
       <c r="P18" s="34"/>
       <c r="Q18" s="34"/>
       <c r="R18" s="34"/>
@@ -1711,10 +1707,7 @@
       <c r="V18" s="15"/>
       <c r="W18" s="15"/>
       <c r="X18" s="15"/>
-      <c r="Y18" s="15">
-        <f>Y17*0.12</f>
-        <v>461.57142857142799</v>
-      </c>
+      <c r="Y18" s="15"/>
       <c r="Z18" s="15"/>
       <c r="AA18" s="26"/>
     </row>
@@ -1732,12 +1725,12 @@
       <c r="I19" s="34"/>
       <c r="J19" s="35"/>
       <c r="K19" s="27"/>
-      <c r="L19" s="59" t="s">
+      <c r="L19" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="M19" s="63"/>
+      <c r="M19" s="57"/>
       <c r="N19" s="38"/>
-      <c r="O19" s="66">
+      <c r="O19" s="58">
         <f>SUM(O13:U18)</f>
         <v>0</v>
       </c>
@@ -1748,9 +1741,9 @@
       <c r="T19" s="37"/>
       <c r="U19" s="38"/>
       <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15"/>
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
@@ -1769,9 +1762,9 @@
       <c r="J20" s="35"/>
       <c r="K20" s="28"/>
       <c r="L20" s="47"/>
-      <c r="M20" s="61"/>
+      <c r="M20" s="55"/>
       <c r="N20" s="47"/>
-      <c r="O20" s="61"/>
+      <c r="O20" s="55"/>
       <c r="P20" s="43"/>
       <c r="Q20" s="43"/>
       <c r="R20" s="43"/>
